--- a/BTTuan7/BaoCaoTestCase.xlsx
+++ b/BTTuan7/BaoCaoTestCase.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThuPhanMem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThuPhanMem\BTTuan7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C7E5D1-A4A2-4338-B888-1E713C03D45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CD270E-3F9B-4FFC-8276-A50976B2E929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Bai1.1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Bai2.1" sheetId="4" r:id="rId4"/>
     <sheet name="Bai2.2" sheetId="5" r:id="rId5"/>
     <sheet name="Bai2.3" sheetId="6" r:id="rId6"/>
+    <sheet name="Bai3.1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="241">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -129,13 +130,680 @@
   </si>
   <si>
     <t>Kỹ thuật (EP/BVA)</t>
+  </si>
+  <si>
+    <t>Ho va ten (*)</t>
+  </si>
+  <si>
+    <t>EP1_V1: Chi chu cai Unicode va dau cach, 2-50 ky tu (VD: "Nguyen Van A")</t>
+  </si>
+  <si>
+    <t>EP1_I1: Rong ("")_x000D_
+EP1_I2: Chua chu so ("Nguyen123")_x000D_
+EP1_I3: Chua ky tu dac biet ("Nguyen@")</t>
+  </si>
+  <si>
+    <t>Ten dang nhap (*)</t>
+  </si>
+  <si>
+    <t>EP2_V1: Bat dau chu thuong, chua a-z/0-9/_, 5-20 ky tu</t>
+  </si>
+  <si>
+    <t>EP2_I1: Rong_x000D_
+EP2_I2: Bat dau bang so ("1user")_x000D_
+EP2_I3: Chu hoa ("User01")_x000D_
+EP2_I4: Ky tu dac biet ("user@01")_x000D_
+EP2_I5: &lt;5 ky tu_x000D_
+EP2_I6: &gt;20 ky tu_x000D_
+EP2_I7: Da ton tai CSDL</t>
+  </si>
+  <si>
+    <t>Email (*)</t>
+  </si>
+  <si>
+    <t>EP3_V1: Dung dinh dang RFC 5322, chua dang ky (VD: newuser@gmail.com)</t>
+  </si>
+  <si>
+    <t>EP3_I1: Rong_x000D_
+EP3_I2: Khong co @ (usermail.com)_x000D_
+EP3_I3: Khong co domain (user@)_x000D_
+EP3_I4: Email da dang ky</t>
+  </si>
+  <si>
+    <t>So dien thoai (*)</t>
+  </si>
+  <si>
+    <t>EP4_V1: Bat dau bang 0, dung 10 chu so (VD: 0987654321)</t>
+  </si>
+  <si>
+    <t>EP4_I1: Rong_x000D_
+EP4_I2: Khong bat dau 0 (1987654321)_x000D_
+EP4_I3: Chua chu cai (098765432a)_x000D_
+EP4_I4: Thieu so - 9 ky tu_x000D_
+EP4_I5: Thua so - 11 ky tu</t>
+  </si>
+  <si>
+    <t>Mat khau (*)</t>
+  </si>
+  <si>
+    <t>EP5_V1: 8-32 ky tu, du hoa+thuong+so+dac biet (VD: Pass@1234)</t>
+  </si>
+  <si>
+    <t>EP5_I1: Rong_x000D_
+EP5_I2: Thieu chu hoa (pass@1234)_x000D_
+EP5_I3: Thieu chu thuong (PASS@1234)_x000D_
+EP5_I4: Thieu chu so (Pass@word)_x000D_
+EP5_I5: Thieu ky tu dac biet (Password1)_x000D_
+EP5_I6: &lt;8 ky tu</t>
+  </si>
+  <si>
+    <t>Xac nhan mat khau (*)</t>
+  </si>
+  <si>
+    <t>EP6_V1: Trung khop voi mat khau da nhap</t>
+  </si>
+  <si>
+    <t>EP6_I1: Rong_x000D_
+EP6_I2: Khong khop voi mat khau</t>
+  </si>
+  <si>
+    <t>Ngay sinh (tuy chon)</t>
+  </si>
+  <si>
+    <t>EP7_V1: dd/MM/yyyy, tuoi 16-99 (VD: 15/03/1990)_x000D_
+EP7_V2: Rong (khong dien - hop le)</t>
+  </si>
+  <si>
+    <t>EP7_I1: Sai dinh dang (1990-03-15)_x000D_
+EP7_I2: Duoi 16 tuoi (01/01/2015)_x000D_
+EP7_I3: Tu 100 tuoi tro len (01/01/1900)</t>
+  </si>
+  <si>
+    <t>Ma gioi thieu (tuy chon)</t>
+  </si>
+  <si>
+    <t>EP8_V1: 8 ky tu [A-Z0-9], co trong CSDL (VD: ABC12345)_x000D_
+EP8_V2: Rong - hop le</t>
+  </si>
+  <si>
+    <t>EP8_I1: Chu thuong (abc12345)_x000D_
+EP8_I2: &lt;8 ky tu (ABC1234)_x000D_
+EP8_I3: &gt;8 ky tu_x000D_
+EP8_I4: Dung format nhung khong ton tai (ZZZZZZZZ)</t>
+  </si>
+  <si>
+    <t>Dong y Dieu khoan (*)</t>
+  </si>
+  <si>
+    <t>EP9_V1: Checkbox duoc tich (true)</t>
+  </si>
+  <si>
+    <t>EP9_I1: Checkbox khong duoc tich (false)</t>
+  </si>
+  <si>
+    <t>Bat buoc; chi chu cai Unicode + dau cach; do dai 2-50</t>
+  </si>
+  <si>
+    <t>Bat buoc; [a-z][a-z0-9_]*; dai 5-20; duy nhat</t>
+  </si>
+  <si>
+    <t>Bat buoc; RFC 5322; chua ton tai CSDL</t>
+  </si>
+  <si>
+    <t>Bat buoc; bat dau 0; dung 10 chu so</t>
+  </si>
+  <si>
+    <t>Bat buoc; 8-32 ky tu; &gt;=1 hoa, &gt;=1 thuong, &gt;=1 so, &gt;=1 dac biet</t>
+  </si>
+  <si>
+    <t>Bat buoc; phai trung khop hoan toan</t>
+  </si>
+  <si>
+    <t>Khong bat buoc; neu nhap: dd/MM/yyyy, tu 16 den duoi 100 tuoi</t>
+  </si>
+  <si>
+    <t>Khong bat buoc; neu nhap: dung 8 ky tu [A-Z0-9]; phai ton tai CSDL</t>
+  </si>
+  <si>
+    <t>Bat buoc phai tich; nut Dang ky bi disabled khi chua tich</t>
+  </si>
+  <si>
+    <t>Bien duoi - do dai toi thieu = 2</t>
+  </si>
+  <si>
+    <t>min-1 = 1 ky tu: "A"</t>
+  </si>
+  <si>
+    <t>INVALID</t>
+  </si>
+  <si>
+    <t>Loi: Qua ngan</t>
+  </si>
+  <si>
+    <t>min = 2 ky tu: "An"</t>
+  </si>
+  <si>
+    <t>VALID</t>
+  </si>
+  <si>
+    <t>Dang ky thanh cong</t>
+  </si>
+  <si>
+    <t>min+1 = 3 ky tu: "Ana"</t>
+  </si>
+  <si>
+    <t>Bien tren - do dai toi da = 50</t>
+  </si>
+  <si>
+    <t>max-1 = 49 ky tu: chui 49 ky tu hop le</t>
+  </si>
+  <si>
+    <t>max = 50 ky tu: chui 50 ky tu hop le</t>
+  </si>
+  <si>
+    <t>max+1 = 51 ky tu: chui 51 ky tu</t>
+  </si>
+  <si>
+    <t>Loi: Qua dai</t>
+  </si>
+  <si>
+    <t>Bien duoi - do dai toi thieu = 5</t>
+  </si>
+  <si>
+    <t>min-1 = 4 ky tu: "user"</t>
+  </si>
+  <si>
+    <t>min = 5 ky tu: "user1"</t>
+  </si>
+  <si>
+    <t>min+1 = 6 ky tu: "user01"</t>
+  </si>
+  <si>
+    <t>Bien tren - do dai toi da = 20</t>
+  </si>
+  <si>
+    <t>max-1 = 19 ky tu</t>
+  </si>
+  <si>
+    <t>max = 20 ky tu</t>
+  </si>
+  <si>
+    <t>max+1 = 21 ky tu</t>
+  </si>
+  <si>
+    <t>Bien duoi - do dai toi thieu = 8</t>
+  </si>
+  <si>
+    <t>min-1 = 7 ky tu: "Pa@1234"</t>
+  </si>
+  <si>
+    <t>min = 8 ky tu: "Pa@12345"</t>
+  </si>
+  <si>
+    <t>min+1 = 9 ky tu: "Pa@123456"</t>
+  </si>
+  <si>
+    <t>Bien tren - do dai toi da = 32</t>
+  </si>
+  <si>
+    <t>max-1 = 31 ky tu</t>
+  </si>
+  <si>
+    <t>max = 32 ky tu</t>
+  </si>
+  <si>
+    <t>max+1 = 33 ky tu</t>
+  </si>
+  <si>
+    <t>Bien duoi - tuoi toi thieu = 16 (ref: 03/03/2026)</t>
+  </si>
+  <si>
+    <t>min-1: 04/03/2010 (15 tuoi 364 ngay)</t>
+  </si>
+  <si>
+    <t>Loi: Chua du 16 tuoi</t>
+  </si>
+  <si>
+    <t>min: 03/03/2010 (dung 16 tuoi)</t>
+  </si>
+  <si>
+    <t>min+1: 02/03/2010 (16 tuoi 1 ngay)</t>
+  </si>
+  <si>
+    <t>Bien tren - tuoi toi da &lt; 100 (ref: 03/03/2026)</t>
+  </si>
+  <si>
+    <t>max-1: 04/03/1926 (99 tuoi 364 ngay)</t>
+  </si>
+  <si>
+    <t>max: 03/03/1926 (dung 100 tuoi)</t>
+  </si>
+  <si>
+    <t>Loi: Tu 100 tuoi tro len</t>
+  </si>
+  <si>
+    <t>max+1: 02/03/1926 (100 tuoi 1 ngay)</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_018</t>
+  </si>
+  <si>
+    <t>Mat khau 33 ky tu (max+1)</t>
+  </si>
+  <si>
+    <t>He thong ShopVN hoat dong._x000D_
+Trang dang ky da mo._x000D_
+Email 'existing@shopvn.com' va username 'user_exist' da ton tai CSDL._x000D_
+Ma gioi thieu 'ABC12345' ton tai CSDL.</t>
+  </si>
+  <si>
+    <t>MAT KHAU: 33 ky tu</t>
+  </si>
+  <si>
+    <t>BVA - max+1</t>
+  </si>
+  <si>
+    <t>Loi: Qua dai (toi da 32 ky tu)</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_019</t>
+  </si>
+  <si>
+    <t>Ngay sinh 04/03/2010 - 15 tuoi 364 ngay (min-1)</t>
+  </si>
+  <si>
+    <t>NGAY SINH: '04/03/2010' -&gt; 15 tuoi 364 ngay vao 03/03/2026</t>
+  </si>
+  <si>
+    <t>BVA - min-1</t>
+  </si>
+  <si>
+    <t>Loi: Phai tu 16 tuoi tro len</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_020</t>
+  </si>
+  <si>
+    <t>Ngay sinh 03/03/2010 - dung 16 tuoi (min)</t>
+  </si>
+  <si>
+    <t>NGAY SINH: '03/03/2010' -&gt; dung 16 tuoi vao 03/03/2026</t>
+  </si>
+  <si>
+    <t>BVA - min</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_021</t>
+  </si>
+  <si>
+    <t>Ngay sinh 02/03/2010 - 16 tuoi 1 ngay (min+1)</t>
+  </si>
+  <si>
+    <t>NGAY SINH: '02/03/2010' -&gt; 16 tuoi 1 ngay vao 03/03/2026</t>
+  </si>
+  <si>
+    <t>BVA - min+1</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_022</t>
+  </si>
+  <si>
+    <t>Ngay sinh 04/03/1926 - 99 tuoi 364 ngay (max-1)</t>
+  </si>
+  <si>
+    <t>NGAY SINH: '04/03/1926' -&gt; 99 tuoi 364 ngay vao 03/03/2026</t>
+  </si>
+  <si>
+    <t>BVA - max-1</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_023</t>
+  </si>
+  <si>
+    <t>Ngay sinh 03/03/1926 - dung 100 tuoi (max)</t>
+  </si>
+  <si>
+    <t>NGAY SINH: '03/03/1926' -&gt; dung 100 tuoi vao 03/03/2026</t>
+  </si>
+  <si>
+    <t>BVA - max</t>
+  </si>
+  <si>
+    <t>Loi: Phai duoi 100 tuoi</t>
+  </si>
+  <si>
+    <t>TC_REG_BVA_024</t>
+  </si>
+  <si>
+    <t>Ngay sinh 02/03/1926 - 100 tuoi 1 ngay (max+1)</t>
+  </si>
+  <si>
+    <t>NGAY SINH: '02/03/1926' -&gt; 100 tuoi 1 ngay vao 03/03/2026</t>
+  </si>
+  <si>
+    <t>&gt;&gt; SPEC - Dac Biet / Server-side</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_001</t>
+  </si>
+  <si>
+    <t>Email da ton tai trong he thong (duplicate)</t>
+  </si>
+  <si>
+    <t>EMAIL: 'existing@shopvn.com' (da co trong CSDL)</t>
+  </si>
+  <si>
+    <t>SPEC</t>
+  </si>
+  <si>
+    <t>Loi: Email da duoc dang ky</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_002</t>
+  </si>
+  <si>
+    <t>Ten dang nhap da ton tai trong he thong</t>
+  </si>
+  <si>
+    <t>TEN DN: 'user_exist' (da co trong CSDL)</t>
+  </si>
+  <si>
+    <t>Loi: Ten dang nhap da ton tai trong he thong</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_003</t>
+  </si>
+  <si>
+    <t>Xac nhan mat khau khong khop</t>
+  </si>
+  <si>
+    <t>MK: 'Pass@1234' | XAC NHAN: 'DifferentPass@99'</t>
+  </si>
+  <si>
+    <t>Loi: Xac nhan mat khau khong khop</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_004</t>
+  </si>
+  <si>
+    <t>Ma gioi thieu hop le va ton tai CSDL</t>
+  </si>
+  <si>
+    <t>MA GIOI THIEU: 'ABC12345' (ton tai trong CSDL)</t>
+  </si>
+  <si>
+    <t>Dang ky thanh cong. Ap dung uu dai.</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_005</t>
+  </si>
+  <si>
+    <t>Ma gioi thieu dung format nhung KHONG ton tai CSDL</t>
+  </si>
+  <si>
+    <t>MA GIOI THIEU: 'ZZZZZZZZ' (khong co trong CSDL)</t>
+  </si>
+  <si>
+    <t>Loi: Ma khong ton tai trong he thong</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_006</t>
+  </si>
+  <si>
+    <t>Ma gioi thieu chua chu thuong (sai format)</t>
+  </si>
+  <si>
+    <t>MA GIOI THIEU: 'abc12345' (chu thuong)</t>
+  </si>
+  <si>
+    <t>Loi: Phai gom dung 8 ky tu chu hoa va so [A-Z0-9]</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_007</t>
+  </si>
+  <si>
+    <t>Khong tich Dong y Dieu khoan - nut bi disabled</t>
+  </si>
+  <si>
+    <t>DONG Y DIEU KHOAN: false (chua tich) | Cac truong khac: hop le</t>
+  </si>
+  <si>
+    <t>Nut [Dang ky] bi disabled. Loi: Bat buoc phai tich dong y.</t>
+  </si>
+  <si>
+    <t>TC_REG_SPEC_008</t>
+  </si>
+  <si>
+    <t>Mat khau thieu ky tu dac biet</t>
+  </si>
+  <si>
+    <t>MAT KHAU: 'Password1' (khong co ky tu dac biet)</t>
+  </si>
+  <si>
+    <t>Loi: Mat khau phai co it nhat 1 ky tu dac biet (!@#$%...)</t>
+  </si>
+  <si>
+    <t>Kết quả thực tế</t>
+  </si>
+  <si>
+    <t>Như mong đợi</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Lab7_DangKy_ShopVN</t>
+  </si>
+  <si>
+    <t>Kiem thu Form Dang Ky Tai Khoan - ShopVN.vn - Black Box EP &amp; BVA</t>
+  </si>
+  <si>
+    <t>Form Dang Ky Tai Khoan</t>
+  </si>
+  <si>
+    <t>Bảng quyết định</t>
+  </si>
+  <si>
+    <t>Điều kiện/Hành động</t>
+  </si>
+  <si>
+    <t>Rule 1</t>
+  </si>
+  <si>
+    <t>Rule 2</t>
+  </si>
+  <si>
+    <t>Rule 3</t>
+  </si>
+  <si>
+    <t>Rule 4</t>
+  </si>
+  <si>
+    <t>Rule 5</t>
+  </si>
+  <si>
+    <t>Rule 6</t>
+  </si>
+  <si>
+    <t>Rule 7</t>
+  </si>
+  <si>
+    <t>Rule 8</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>+ OTP bổ sung</t>
+  </si>
+  <si>
+    <t>TC_DT_R1</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>20:00 Thứ 3 (ngoài giờ)</t>
+  </si>
+  <si>
+    <t>Cùng NH</t>
+  </si>
+  <si>
+    <t>Miễn 100% phí</t>
+  </si>
+  <si>
+    <t>TC_DT_R2</t>
+  </si>
+  <si>
+    <t>10:00 Thứ 3 (giờ HC)</t>
+  </si>
+  <si>
+    <t>Khác NH</t>
+  </si>
+  <si>
+    <t>Phí 3.300đ</t>
+  </si>
+  <si>
+    <t>TC_DT_R3</t>
+  </si>
+  <si>
+    <t>Phí 8.800đ</t>
+  </si>
+  <si>
+    <t>TC_DT_R4</t>
+  </si>
+  <si>
+    <t>Không VIP</t>
+  </si>
+  <si>
+    <t>TC_DT_R5</t>
+  </si>
+  <si>
+    <t>TC_DT_R6</t>
+  </si>
+  <si>
+    <t>Phí 11.000đ</t>
+  </si>
+  <si>
+    <t>TC_DT_R7</t>
+  </si>
+  <si>
+    <t>Phí 16.500đ</t>
+  </si>
+  <si>
+    <t>TC_DT_R8</t>
+  </si>
+  <si>
+    <t>Phí 11.000đ + OT</t>
+  </si>
+  <si>
+    <t>Loại TK</t>
+  </si>
+  <si>
+    <t>Giờ GD</t>
+  </si>
+  <si>
+    <t>Ngân hàng</t>
+  </si>
+  <si>
+    <t>Số tiền (triệu)</t>
+  </si>
+  <si>
+    <t>Kết quả  mong đợi (phí + OTP?)</t>
+  </si>
+  <si>
+    <t>KQ thực tế</t>
+  </si>
+  <si>
+    <t>P/F</t>
+  </si>
+  <si>
+    <t>Rule 9</t>
+  </si>
+  <si>
+    <t>Rule 10</t>
+  </si>
+  <si>
+    <t>Rule 11</t>
+  </si>
+  <si>
+    <t>Rule 12</t>
+  </si>
+  <si>
+    <t>Rule 13</t>
+  </si>
+  <si>
+    <t>Rule 14</t>
+  </si>
+  <si>
+    <t>Rule 15</t>
+  </si>
+  <si>
+    <t>Rule 16</t>
+  </si>
+  <si>
+    <t>C1: VIP?</t>
+  </si>
+  <si>
+    <t>C2: Giờ HC?</t>
+  </si>
+  <si>
+    <t>C3: Cùng NH?</t>
+  </si>
+  <si>
+    <t>C4: &gt; 500 triệu?</t>
+  </si>
+  <si>
+    <t>A1: Miễn phí</t>
+  </si>
+  <si>
+    <t>A2: 3.300đ</t>
+  </si>
+  <si>
+    <t>A3: 8.800đ</t>
+  </si>
+  <si>
+    <t>A4: 11.000đ</t>
+  </si>
+  <si>
+    <t>A5: 16.500đ</t>
+  </si>
+  <si>
+    <t>Rút gọn: Bất kỳ quy tắc nào có C4 = Y (&gt; 500 triệu) đều cộng thêm OTP</t>
+  </si>
+  <si>
+    <t>Điều kiện / Hành động</t>
+  </si>
+  <si>
+    <t>+ OTP (nếu C4=Y)</t>
+  </si>
+  <si>
+    <t>Câu 1: Thêm C5 "Tài khoản mới &lt; 6 tháng" thì số quy tắc tăng gấp đôi từ 8 lên 16. Cách quản lý: dùng ký hiệu - (không quan tâm) cho những quy tắc mà C5 không ảnh hưởng đến hành động, gộp các quy tắc có cùng kết quả để rút gọn bảng.</t>
+  </si>
+  <si>
+    <t>Câu 2: C4 (&gt; 500 triệu) ảnh hưởng cắt ngang tất cả quy tắc → kỹ thuật Cause-Effect Graph (biểu đồ nguyên nhân – kết quả) biểu diễn gọn hơn, vì nó thể hiện C4 như một điều kiện phụ chồng lên tất cả nhánh, thay vì phải nhân đôi số cột trong bảng quyết định.</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +832,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -173,7 +847,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -449,32 +1123,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -482,20 +1178,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -512,23 +1196,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -542,6 +1211,77 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -857,583 +1597,2110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A911C451-4F5E-414A-9389-A33A7B867661}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="47.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="10">
-        <v>1</v>
-      </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="20">
-        <v>46049</v>
-      </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22" t="s">
+      <c r="E6" s="26">
+        <v>46084</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="H6" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="H9" s="35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+    </row>
+    <row r="10" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="H10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="I10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="J10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="K10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="L10" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+    <row r="11" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H20" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H23" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H26" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="J26" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="K28" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H29" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="K29" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29" s="31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L31" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H32" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="K32" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="K33" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="L34" s="31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+    <row r="37" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B37" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C37" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D37" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E37" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F37" s="37" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="G37" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H41" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F43" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H43" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H45" s="31"/>
+    </row>
+    <row r="46" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H46" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E47" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F50" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E51" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="G51" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="E52" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="G52" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G53" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H53" s="31" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="23">
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="I29:I31"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="I26:I28"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029BB07F-91F7-4C77-BBBC-943BDBDA5479}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="26">
         <v>46049</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="27"/>
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+    </row>
+    <row r="10" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q11" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q12" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q20" s="16"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="16"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+    <row r="39" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="B39" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" s="16">
+        <v>200</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="16">
+        <v>200</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="16">
+        <v>200</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="16">
+        <v>200</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="16">
+        <v>200</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E45" s="16">
+        <v>200</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E46" s="16">
+        <v>200</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A47" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="16">
+        <v>600</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+    </row>
+    <row r="52" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1443,287 +3710,287 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="26">
         <v>46049</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="27"/>
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1734,287 +4001,287 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="26">
         <v>46049</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="27"/>
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2025,287 +4292,287 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="26">
         <v>46049</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="27"/>
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2316,288 +4583,297 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="26">
         <v>46049</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="27"/>
+      <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="25"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993B51D7-01A3-4330-BCFF-E3274809A9A8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BTTuan7/BaoCaoTestCase.xlsx
+++ b/BTTuan7/BaoCaoTestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThuPhanMem\BTTuan7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CD270E-3F9B-4FFC-8276-A50976B2E929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F156EF-D22F-47DA-9D8A-C24C265EDC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="253">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -595,9 +595,6 @@
     <t>Trạng thái</t>
   </si>
   <si>
-    <t>Lab7_DangKy_ShopVN</t>
-  </si>
-  <si>
     <t>Kiem thu Form Dang Ky Tai Khoan - ShopVN.vn - Black Box EP &amp; BVA</t>
   </si>
   <si>
@@ -797,6 +794,45 @@
   </si>
   <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Trạng thái ban đầu</t>
+  </si>
+  <si>
+    <t>Hành động/Sự kiện</t>
+  </si>
+  <si>
+    <t>Trạng thái kết thúc mong đợi</t>
+  </si>
+  <si>
+    <t>Dữ liệu đặc biệt</t>
+  </si>
+  <si>
+    <t>Hợp lệ ?</t>
+  </si>
+  <si>
+    <t>Kết quả mong đợi chi tiết</t>
+  </si>
+  <si>
+    <t>Lab7_1.1_DangKy_ShopVN</t>
+  </si>
+  <si>
+    <t>Lab7_1.2_Bank</t>
+  </si>
+  <si>
+    <t>Kiểm thử Bảng Quyết Định – Chính Sách Phí Dịch Vụ Ngân Hàng</t>
+  </si>
+  <si>
+    <t>Decision Table</t>
+  </si>
+  <si>
+    <t>Lab7_1.3_HotelRoom</t>
+  </si>
+  <si>
+    <t>Kiểm thử Chuyển Trạng Thái – Hệ Thống Đặt Phòng Khách Sạn</t>
+  </si>
+  <si>
+    <t>StateDiagram</t>
   </si>
 </sst>
 </file>
@@ -1620,14 +1656,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -1684,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="29"/>
@@ -2672,14 +2708,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -2736,7 +2772,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>12</v>
+        <v>249</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="29"/>
@@ -2744,7 +2780,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
@@ -2757,286 +2793,286 @@
     </row>
     <row r="10" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="C10" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="F10" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="G10" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="H10" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="I10" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="15" t="s">
-        <v>185</v>
-      </c>
       <c r="J10" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="K10" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="L10" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="M10" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="O10" s="15" t="s">
+      <c r="P10" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="Q10" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="K11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="N11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="O11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="P11" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="Q11" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="G12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="H12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="I12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="J12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="N12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="O12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="P12" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="Q12" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="O12" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="P12" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="F13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="I13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="J13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="N13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="P13" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="Q13" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="D14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="F14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="H14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="J14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="K14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="L14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="N14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="O14" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="O14" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="P14" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q14" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
@@ -3051,25 +3087,25 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
@@ -3080,7 +3116,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -3089,27 +3125,27 @@
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
       <c r="H17" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O17" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -3122,10 +3158,10 @@
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
@@ -3134,7 +3170,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3151,190 +3187,190 @@
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
       <c r="P19" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q19" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I20" s="16"/>
       <c r="J20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K20" s="16"/>
       <c r="L20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M20" s="16"/>
       <c r="N20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q20" s="16"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>183</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="F25" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="G25" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E25" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="H25" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C26" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="E26" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="G26" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="D27" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E27" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="H27" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -3345,15 +3381,15 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
@@ -3361,23 +3397,23 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -3385,13 +3421,13 @@
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
       <c r="G32" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -3400,33 +3436,33 @@
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
       <c r="H33" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -3439,238 +3475,238 @@
         <v>24</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="D39" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="E39" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="F39" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="G39" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="H39" s="12" t="s">
         <v>216</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="C40" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="D40" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="E40" s="16">
         <v>200</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="D41" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="E41" s="16">
         <v>200</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B42" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>193</v>
-      </c>
       <c r="D42" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E42" s="16">
         <v>200</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>203</v>
-      </c>
       <c r="C43" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E43" s="16">
         <v>200</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C44" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>193</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>194</v>
       </c>
       <c r="E44" s="16">
         <v>200</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C45" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="E45" s="16">
         <v>200</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" s="16">
         <v>200</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C47" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="E47" s="16">
         <v>600</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>171</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
@@ -3680,7 +3716,7 @@
     </row>
     <row r="52" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
@@ -3707,7 +3743,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E447681E-DE3A-44C2-B0D1-3B8EA5BE633F}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -3728,14 +3764,14 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -3785,202 +3821,107 @@
         <v>10</v>
       </c>
       <c r="E6" s="26">
-        <v>46049</v>
+        <v>46084</v>
       </c>
       <c r="F6" s="27"/>
       <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="29"/>
       <c r="K6" s="30"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>22</v>
-      </c>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="13"/>
+    </row>
+    <row r="9" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/BTTuan7/BaoCaoTestCase.xlsx
+++ b/BTTuan7/BaoCaoTestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThuPhanMem\BTTuan7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F156EF-D22F-47DA-9D8A-C24C265EDC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F556B2EB-CD07-4108-8D46-E951561AA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="338">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -833,6 +833,261 @@
   </si>
   <si>
     <t>StateDiagram</t>
+  </si>
+  <si>
+    <t>TC_ST_01</t>
+  </si>
+  <si>
+    <t>S0: KHỞI_TẠO</t>
+  </si>
+  <si>
+    <t>Xác nhận đặt phòng</t>
+  </si>
+  <si>
+    <t>S1: CHỜ_THANH_TOÁN</t>
+  </si>
+  <si>
+    <t>Đặt phòng hợp lệ</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>Hệ thống tạo booking, bắt đầu đếm ngược 30 phút</t>
+  </si>
+  <si>
+    <t>TC_ST_02</t>
+  </si>
+  <si>
+    <t>Thanh toán online thành công</t>
+  </si>
+  <si>
+    <t>S2: ĐÃ_THANH_TOÁN</t>
+  </si>
+  <si>
+    <t>TT trong 30 phút</t>
+  </si>
+  <si>
+    <t>Hệ thống ghi nhận thanh toán, chờ KS xác nhận</t>
+  </si>
+  <si>
+    <t>TC_ST_03</t>
+  </si>
+  <si>
+    <t>Timeout 30 phút</t>
+  </si>
+  <si>
+    <t>S9: HẾT_HẠN</t>
+  </si>
+  <si>
+    <t>Không TT đúng hạn</t>
+  </si>
+  <si>
+    <t>Đặt phòng tự động hủy, thông báo khách</t>
+  </si>
+  <si>
+    <t>TC_ST_04</t>
+  </si>
+  <si>
+    <t>Khách hủy đặt phòng</t>
+  </si>
+  <si>
+    <t>S6: ĐÃ_HỦY</t>
+  </si>
+  <si>
+    <t>Chưa thanh toán</t>
+  </si>
+  <si>
+    <t>Hủy thành công, không hoàn tiền (chưa TT)</t>
+  </si>
+  <si>
+    <t>TC_ST_05</t>
+  </si>
+  <si>
+    <t>Khách sạn xác nhận còn phòng</t>
+  </si>
+  <si>
+    <t>S3: ĐÃ_XÁC_NHẬN</t>
+  </si>
+  <si>
+    <t>KS có phòng trống</t>
+  </si>
+  <si>
+    <t>Booking được xác nhận, khách nhận thông báo</t>
+  </si>
+  <si>
+    <t>TC_ST_06</t>
+  </si>
+  <si>
+    <t>Khách sạn từ chối (hết phòng)</t>
+  </si>
+  <si>
+    <t>KS hết phòng</t>
+  </si>
+  <si>
+    <t>Hủy và chuyển sang CHỜ_HOÀN_TIỀN nếu đã TT</t>
+  </si>
+  <si>
+    <t>TC_ST_07</t>
+  </si>
+  <si>
+    <t>Check-in</t>
+  </si>
+  <si>
+    <t>S4: ĐANG_LƯU_TRÚ</t>
+  </si>
+  <si>
+    <t>Đúng ngày check-in</t>
+  </si>
+  <si>
+    <t>Trạng thái chuyển sang đang lưu trú</t>
+  </si>
+  <si>
+    <t>TC_ST_08</t>
+  </si>
+  <si>
+    <t>Hủy trong thời hạn miễn phí</t>
+  </si>
+  <si>
+    <t>Trước deadline hủy</t>
+  </si>
+  <si>
+    <t>Hủy thành công, chuyển sang CHỜ_HOÀN_TIỀN</t>
+  </si>
+  <si>
+    <t>TC_ST_09</t>
+  </si>
+  <si>
+    <t>Hủy sau thời hạn miễn phí</t>
+  </si>
+  <si>
+    <t>S7: CHỜ_HOÀN_TIỀN</t>
+  </si>
+  <si>
+    <t>Sau deadline hủy</t>
+  </si>
+  <si>
+    <t>Hủy, hoàn tiền một phần (trừ phí phạt)</t>
+  </si>
+  <si>
+    <t>TC_ST_10</t>
+  </si>
+  <si>
+    <t>Check-out</t>
+  </si>
+  <si>
+    <t>S5: HOÀN_THÀNH</t>
+  </si>
+  <si>
+    <t>Đúng ngày check-out</t>
+  </si>
+  <si>
+    <t>Đặt phòng hoàn tất thành công</t>
+  </si>
+  <si>
+    <t>TC_ST_11</t>
+  </si>
+  <si>
+    <t>Yêu cầu hoàn tiền</t>
+  </si>
+  <si>
+    <t>Đã thanh toán trước</t>
+  </si>
+  <si>
+    <t>Hệ thống ghi nhận yêu cầu, chờ xử lý</t>
+  </si>
+  <si>
+    <t>TC_ST_12</t>
+  </si>
+  <si>
+    <t>Hoàn tiền thành công</t>
+  </si>
+  <si>
+    <t>S8: ĐÃ_HOÀN_TIỀN</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Tiền về tài khoản khách, kết thúc</t>
+  </si>
+  <si>
+    <t>TC_ST_INV01</t>
+  </si>
+  <si>
+    <t>Thanh toán ngay (bỏ qua xác nhận)</t>
+  </si>
+  <si>
+    <t>Vẫn ở S0</t>
+  </si>
+  <si>
+    <t>Chưa qua S1</t>
+  </si>
+  <si>
+    <t>Không</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối, báo lỗi "Chưa xác nhận đặt phòng"</t>
+  </si>
+  <si>
+    <t>TC_ST_INV02</t>
+  </si>
+  <si>
+    <t>Yêu cầu hủy đặt phòng</t>
+  </si>
+  <si>
+    <t>Vẫn ở S5</t>
+  </si>
+  <si>
+    <t>Đã check-out</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối, báo lỗi "Booking đã hoàn tất"</t>
+  </si>
+  <si>
+    <t>TC_ST_INV03</t>
+  </si>
+  <si>
+    <t>Thanh toán lại để kích hoạt</t>
+  </si>
+  <si>
+    <t>Vẫn ở S9</t>
+  </si>
+  <si>
+    <t>Booking đã hết hạn</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối, báo lỗi "Đặt phòng đã hết hạn"</t>
+  </si>
+  <si>
+    <t>TC_ST_INV04</t>
+  </si>
+  <si>
+    <t>Hủy đặt phòng (đang ở khách sạn)</t>
+  </si>
+  <si>
+    <t>Vẫn ở S4</t>
+  </si>
+  <si>
+    <t>Đang lưu trú</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối, báo lỗi "Không thể hủy khi đang lưu trú"</t>
+  </si>
+  <si>
+    <t>TC_ST_INV05</t>
+  </si>
+  <si>
+    <t>Check-out (bỏ qua check-in)</t>
+  </si>
+  <si>
+    <t>Vẫn ở S3</t>
+  </si>
+  <si>
+    <t>Chưa check-in</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối, báo lỗi "Chưa check-in"</t>
   </si>
 </sst>
 </file>
@@ -3743,7 +3998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E447681E-DE3A-44C2-B0D1-3B8EA5BE633F}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -3860,68 +4115,396 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+    <row r="10" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>337</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/BTTuan7/BaoCaoTestCase.xlsx
+++ b/BTTuan7/BaoCaoTestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThuPhanMem\BTTuan7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F556B2EB-CD07-4108-8D46-E951561AA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E3955A-CC65-4B04-A63F-F75D86C25A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
   </bookViews>

--- a/BTTuan7/BaoCaoTestCase.xlsx
+++ b/BTTuan7/BaoCaoTestCase.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemThuPhanMem\BTTuan7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E3955A-CC65-4B04-A63F-F75D86C25A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73B5A12-1111-424C-BA6C-C746AD993D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{4E97708E-8CD6-4174-A6FD-6089F64AF7FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Bai1.1" sheetId="1" r:id="rId1"/>
     <sheet name="Bai1.2" sheetId="2" r:id="rId2"/>
     <sheet name="Bai1.3" sheetId="3" r:id="rId3"/>
-    <sheet name="Bai2.1" sheetId="4" r:id="rId4"/>
-    <sheet name="Bai2.2" sheetId="5" r:id="rId5"/>
-    <sheet name="Bai2.3" sheetId="6" r:id="rId6"/>
-    <sheet name="Bai3.1" sheetId="7" r:id="rId7"/>
+    <sheet name="Bai2.2" sheetId="5" r:id="rId4"/>
+    <sheet name="Bai2.3" sheetId="6" r:id="rId5"/>
+    <sheet name="Bai3.1" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="552">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -484,9 +483,6 @@
     <t>NGAY SINH: '02/03/1926' -&gt; 100 tuoi 1 ngay vao 03/03/2026</t>
   </si>
   <si>
-    <t>&gt;&gt; SPEC - Dac Biet / Server-side</t>
-  </si>
-  <si>
     <t>TC_REG_SPEC_001</t>
   </si>
   <si>
@@ -1088,13 +1084,734 @@
   </si>
   <si>
     <t>Hệ thống từ chối, báo lỗi "Chưa check-in"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Câu 1: </t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Đường đi</t>
+  </si>
+  <si>
+    <t>Transitions covered</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>S0→S1→S2→S3→S4→S5</t>
+  </si>
+  <si>
+    <t>T01, T02, T05, T07, T10</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>S0→S1→S9</t>
+  </si>
+  <si>
+    <t>T03</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>S0→S1→S6→S7→S8</t>
+  </si>
+  <si>
+    <t>T04, T11, T12</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>S0→S1→S2→S6→S7→S8</t>
+  </si>
+  <si>
+    <t>T06 (T11, T12 tái dùng)</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>S0→S1→S2→S3→S7→S8</t>
+  </si>
+  <si>
+    <t>T08, T09</t>
+  </si>
+  <si>
+    <t>Với 12 chuyển đổi hợp lệ, có thể gộp thành 5 đường đi (test path) bao phủ toàn bộ:</t>
+  </si>
+  <si>
+    <t>Câu 2:</t>
+  </si>
+  <si>
+    <t>→ Tối thiểu 5 test case là đủ cho all-transitions coverage.</t>
+  </si>
+  <si>
+    <t>Test timeout S9 không cần đợi 30 phút:</t>
+  </si>
+  <si>
+    <r>
+      <t>Mock/Stub thời gian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: Inject Clock giả vào hệ thống, set thời gian nhảy lên +31 phút ngay lập tức</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cấu hình timeout rút gọn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: Đặt timeout = 5 giây trong môi trường test (qua config/env variable), kiểm tra S1→S9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Trigger thủ công</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: Gọi trực tiếp method/API expireBooking(bookingId) thay vì chờ scheduler</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Time-based testing framework</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: Dùng thư viện như Mockito mock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>System.currentTimeMillis()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>java.time.Clock</t>
+    </r>
+  </si>
+  <si>
+    <t>Dùng các kỹ thuật sau:</t>
+  </si>
+  <si>
+    <t>Kiểm Thử Đăng Nhập – saucedemo.com với DataProvider</t>
+  </si>
+  <si>
+    <t>Lab7_2.2_Saucedemo</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>TC01</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản standard hợp lệ</t>
+  </si>
+  <si>
+    <t>Trình duyệt mở saucedemo.com</t>
+  </si>
+  <si>
+    <t>user: standard_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>EP – lớp hợp lệ</t>
+  </si>
+  <si>
+    <t>Chuyển sang /inventory.html</t>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản problem_user</t>
+  </si>
+  <si>
+    <t>user: problem_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>Chuyển sang /inventory.html (UI sản phẩm lỗi)</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản performance_glitch_user</t>
+  </si>
+  <si>
+    <t>user: performance_glitch_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>Chuyển sang /inventory.html (tải chậm)</t>
+  </si>
+  <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản error_user</t>
+  </si>
+  <si>
+    <t>user: error_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC05</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản visual_user</t>
+  </si>
+  <si>
+    <t>user: visual_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản bị khóa</t>
+  </si>
+  <si>
+    <t>user: locked_out_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>EP – lớp không hợp lệ</t>
+  </si>
+  <si>
+    <t>Hiện lỗi "Sorry, this user has been locked out"</t>
+  </si>
+  <si>
+    <t>TC07</t>
+  </si>
+  <si>
+    <t>Sai mật khẩu</t>
+  </si>
+  <si>
+    <t>user: standard_user / pass: wrong_password</t>
+  </si>
+  <si>
+    <t>Hiện lỗi "Username and password do not match"</t>
+  </si>
+  <si>
+    <t>TC08</t>
+  </si>
+  <si>
+    <t>Sai username</t>
+  </si>
+  <si>
+    <t>user: wrong_user / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC09</t>
+  </si>
+  <si>
+    <t>Sai cả username lẫn password</t>
+  </si>
+  <si>
+    <t>user: wrong_user / pass: wrong_password</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>Username chữ hoa (case-sensitive)</t>
+  </si>
+  <si>
+    <t>user: STANDARD_USER / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>Bỏ trống username</t>
+  </si>
+  <si>
+    <t>user: (trống) / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>BVA – giá trị biên rỗng</t>
+  </si>
+  <si>
+    <t>Hiện lỗi "Username is required"</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>Bỏ trống password</t>
+  </si>
+  <si>
+    <t>user: standard_user / pass: (trống)</t>
+  </si>
+  <si>
+    <t>Hiện lỗi "Password is required"</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>Bỏ trống cả hai trường</t>
+  </si>
+  <si>
+    <t>user: (trống) / pass: (trống)</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>Khoảng trắng đầu username</t>
+  </si>
+  <si>
+    <t>user: " standard_user" / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>Khoảng trắng cuối username</t>
+  </si>
+  <si>
+    <t>user: "standard_user " / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>Khoảng trắng cả đầu/cuối username</t>
+  </si>
+  <si>
+    <t>user: " standard_user " / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t>Username là XSS script tag</t>
+  </si>
+  <si>
+    <t>Kiểm thử bảo mật</t>
+  </si>
+  <si>
+    <t>Hiện lỗi, không thực thi script</t>
+  </si>
+  <si>
+    <t>TC18</t>
+  </si>
+  <si>
+    <t>Username là SQL injection</t>
+  </si>
+  <si>
+    <t>Hiện lỗi, không bypass đăng nhập</t>
+  </si>
+  <si>
+    <t>TC19</t>
+  </si>
+  <si>
+    <t>Username dạng email</t>
+  </si>
+  <si>
+    <t>user: user@domain.com / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>Username null</t>
+  </si>
+  <si>
+    <t>user: null / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>Giá trị đặc biệt</t>
+  </si>
+  <si>
+    <t>Hệ thống xử lý an toàn, không crash</t>
+  </si>
+  <si>
+    <t>TC21</t>
+  </si>
+  <si>
+    <t>Password null</t>
+  </si>
+  <si>
+    <t>user: standard_user / pass: null</t>
+  </si>
+  <si>
+    <t>user: &lt;script&gt;alert(1)&lt;/script&gt; / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>user: ' OR '1'='1 / pass: secret_sauce</t>
+  </si>
+  <si>
+    <t>TC22</t>
+  </si>
+  <si>
+    <t>Kiểm tra cơ chế chụp screenshot tự động khi test FAIL – dùng tài khoản bị khóa nhưng kỳ vọng đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>user: locked_out_user / pass: secret_sauce / ketQuaMongDoi: THANH_CONG</t>
+  </si>
+  <si>
+    <t>Demo FAIL – kiểm thử cơ chế báo lỗi</t>
+  </si>
+  <si>
+    <t>FAIL – Không chuyển sang /inventory.html, screenshot tự động lưu vào /screenshots/</t>
+  </si>
+  <si>
+    <t>Tiêu đề test case</t>
+  </si>
+  <si>
+    <t>Tiền điều kiện</t>
+  </si>
+  <si>
+    <t>Bước thực hiện (mô tả ngắn)</t>
+  </si>
+  <si>
+    <t>TC_CART_001</t>
+  </si>
+  <si>
+    <t>Thêm 1 sản phẩm – badge = 1</t>
+  </si>
+  <si>
+    <t>Nhấn "Add to cart" cho "Sauce Labs Backpack" → mở giỏ hàng</t>
+  </si>
+  <si>
+    <t>Badge hiển thị 1; giỏ hàng có đúng 1 sản phẩm "Sauce Labs Backpack"</t>
+  </si>
+  <si>
+    <t>TC_CART_002</t>
+  </si>
+  <si>
+    <t>Thêm 3 sản phẩm – badge = 3</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập; đang ở trang Inventory</t>
+  </si>
+  <si>
+    <t>Nhấn "Add to cart" cho 3 sản phẩm đầu tiên → mở giỏ hàng</t>
+  </si>
+  <si>
+    <t>Badge hiển thị 3; giỏ hàng có đúng 3 sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_CART_003</t>
+  </si>
+  <si>
+    <t>Thêm tất cả 6 sản phẩm – badge = 6</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập; đang ở trang Inventory (6 sản phẩm)</t>
+  </si>
+  <si>
+    <t>Nhấn "Add to cart" cho tất cả 6 sản phẩm → mở giỏ hàng</t>
+  </si>
+  <si>
+    <t>Badge hiển thị 6; giỏ hàng có đúng 6 sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_CART_004</t>
+  </si>
+  <si>
+    <t>Xóa 1 sản phẩm – badge giảm</t>
+  </si>
+  <si>
+    <t>Đã thêm 2 sản phẩm vào giỏ; đang ở trang Cart</t>
+  </si>
+  <si>
+    <t>Nhấn "Remove" cho "Sauce Labs Backpack"</t>
+  </si>
+  <si>
+    <t>Giỏ hàng còn 1 sản phẩm; "Sauce Labs Backpack" không còn; "Sauce Labs Bike Light" vẫn còn</t>
+  </si>
+  <si>
+    <t>TC_CART_005</t>
+  </si>
+  <si>
+    <t>Xóa hết sản phẩm – giỏ trống</t>
+  </si>
+  <si>
+    <t>Đã thêm 3 sản phẩm; đang ở trang Cart</t>
+  </si>
+  <si>
+    <t>Nhấn "Remove" cho tất cả sản phẩm</t>
+  </si>
+  <si>
+    <t>Giỏ hàng trống; badge về 0</t>
+  </si>
+  <si>
+    <t>TC_CART_006</t>
+  </si>
+  <si>
+    <t>Giỏ trống – nút Checkout vẫn hiển thị</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập; chưa thêm sản phẩm</t>
+  </si>
+  <si>
+    <t>Mở trang Cart khi giỏ trống</t>
+  </si>
+  <si>
+    <t>Trang Cart tải được; nút Checkout hiển thị (không bị disable)</t>
+  </si>
+  <si>
+    <t>TC_CART_007</t>
+  </si>
+  <si>
+    <t>Sort Name A→Z – đúng thứ tự</t>
+  </si>
+  <si>
+    <t>Chọn sắp xếp "Name (A to Z)"</t>
+  </si>
+  <si>
+    <t>Danh sách 6 sản phẩm hiển thị theo thứ tự tên từ A đến Z</t>
+  </si>
+  <si>
+    <t>TC_CART_008</t>
+  </si>
+  <si>
+    <t>Sort Name Z→A – đúng thứ tự</t>
+  </si>
+  <si>
+    <t>Chọn sắp xếp "Name (Z to A)"</t>
+  </si>
+  <si>
+    <t>Danh sách sản phẩm hiển thị theo thứ tự tên từ Z đến A</t>
+  </si>
+  <si>
+    <t>TC_CART_009</t>
+  </si>
+  <si>
+    <t>Sort giá tăng dần – đúng thứ tự</t>
+  </si>
+  <si>
+    <t>Chọn sắp xếp "Price (low to high)"</t>
+  </si>
+  <si>
+    <t>Danh sách sản phẩm hiển thị theo giá tăng dần</t>
+  </si>
+  <si>
+    <t>TC_CART_010</t>
+  </si>
+  <si>
+    <t>Sort giá giảm dần – đúng thứ tự</t>
+  </si>
+  <si>
+    <t>Chọn sắp xếp "Price (high to low)"</t>
+  </si>
+  <si>
+    <t>Danh sách sản phẩm hiển thị theo giá giảm dần</t>
+  </si>
+  <si>
+    <t>TC_CART_011</t>
+  </si>
+  <si>
+    <t>Kiểm tra tổng tiền chính xác</t>
+  </si>
+  <si>
+    <t>Đã thêm 3 sản phẩm (Backpack $29.99, Bike Light $9.99, Bolt T-Shirt $15.99)</t>
+  </si>
+  <si>
+    <t>Checkout → Step 2 → kiểm tra Item total, Tax, Total</t>
+  </si>
+  <si>
+    <t>Item total = $55.97; Tax = Item total × 8%; Total = Item total + Tax (sai số ≤ 0.01)</t>
+  </si>
+  <si>
+    <t>TC_CART_012</t>
+  </si>
+  <si>
+    <t>Checkout – thiếu First Name → lỗi</t>
+  </si>
+  <si>
+    <t>Đã thêm sản phẩm; đang ở Checkout Step 1</t>
+  </si>
+  <si>
+    <t>Điền Last Name và Zip Code, bỏ trống First Name → nhấn Continue</t>
+  </si>
+  <si>
+    <t>Không chuyển sang Step 2; hiển thị lỗi "First Name is required"</t>
+  </si>
+  <si>
+    <t>TC_CART_013</t>
+  </si>
+  <si>
+    <t>Checkout – thiếu Last Name → lỗi</t>
+  </si>
+  <si>
+    <t>Điền First Name và Zip Code, bỏ trống Last Name → nhấn Continue</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi "Last Name is required"</t>
+  </si>
+  <si>
+    <t>TC_CART_014</t>
+  </si>
+  <si>
+    <t>Checkout – thiếu Zip Code → lỗi</t>
+  </si>
+  <si>
+    <t>Điền First Name và Last Name, bỏ trống Zip Code → nhấn Continue</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi "Postal Code is required"</t>
+  </si>
+  <si>
+    <t>TC_CART_015</t>
+  </si>
+  <si>
+    <t>Checkout đầy đủ thông tin → thành công</t>
+  </si>
+  <si>
+    <t>Đã thêm sản phẩm; đang ở trang Cart</t>
+  </si>
+  <si>
+    <t>Checkout → điền đủ thông tin → Continue → Finish</t>
+  </si>
+  <si>
+    <t>Hiển thị trang "Thank you for your order!"</t>
+  </si>
+  <si>
+    <t>TC_CART_016</t>
+  </si>
+  <si>
+    <t>Sau checkout complete – giỏ hàng reset về 0</t>
+  </si>
+  <si>
+    <t>Đã thêm 3 sản phẩm; hoàn tất đặt hàng</t>
+  </si>
+  <si>
+    <t>Nhấn "Back Home" sau khi hoàn tất đặt hàng</t>
+  </si>
+  <si>
+    <t>Quay về Inventory; badge = 0 (giỏ hàng được reset)</t>
+  </si>
+  <si>
+    <t>TC_CART_017</t>
+  </si>
+  <si>
+    <t>Cancel Step 1 → quay về cart.html</t>
+  </si>
+  <si>
+    <t>Nhấn "Cancel" tại Step 1</t>
+  </si>
+  <si>
+    <t>TC_CART_018</t>
+  </si>
+  <si>
+    <t>Cancel Step 2 → quay về inventory.html</t>
+  </si>
+  <si>
+    <t>Đã thêm sản phẩm; đang ở Checkout Step 2</t>
+  </si>
+  <si>
+    <t>Hoàn tất Step 1 → nhấn "Cancel" tại Step 2</t>
+  </si>
+  <si>
+    <t>TC_CART_019</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm trong giỏ khớp với đã thêm</t>
+  </si>
+  <si>
+    <t>Thêm "Sauce Labs Backpack" và "Sauce Labs Fleece Jacket" → mở giỏ</t>
+  </si>
+  <si>
+    <t>Giỏ hàng có đúng 2 sản phẩm; tên khớp hoàn toàn với sản phẩm đã thêm</t>
+  </si>
+  <si>
+    <t>TC_CART_020</t>
+  </si>
+  <si>
+    <t>Continue Shopping → quay về inventory.html</t>
+  </si>
+  <si>
+    <t>Đã thêm 1 sản phẩm; đang ở trang Cart</t>
+  </si>
+  <si>
+    <t>Nhấn "Continue Shopping"</t>
+  </si>
+  <si>
+    <t>Quay về trang Inventory; badge vẫn = 1 (sản phẩm chưa bị xóa)</t>
+  </si>
+  <si>
+    <t>TC_CART_021</t>
+  </si>
+  <si>
+    <t>problem_user – kiểm tra bug thêm &amp; xóa giỏ hàng</t>
+  </si>
+  <si>
+    <t>Đang ở trình duyệt; chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Badge sau thêm = 1; badge sau xóa = 0 (ghi nhận bug nếu không xóa được)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập với standard_user; đang ở trang Inventory</t>
+  </si>
+  <si>
+    <t>Quay về trang Cart (cart.html)</t>
+  </si>
+  <si>
+    <t>Quay về trang Inventory (inventory.html)</t>
+  </si>
+  <si>
+    <t>Đăng nhập bằng problem_user → thêm sản phẩm → xóa sản phẩm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1128,6 +1845,27 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1455,7 +2193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1503,6 +2241,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1530,49 +2309,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1589,6 +2339,148 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39077</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>231002</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>165880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0992C9FE-D2F8-44BE-9DF1-D40094F6E7FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1367692"/>
+          <a:ext cx="15461233" cy="3839111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>478518</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>172359</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>330490</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B2AAA31-36C5-4C3E-AB37-7EF14CAB7C33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11182804" y="1288145"/>
+          <a:ext cx="10080625" cy="6889131"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>172357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>792834</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>113745</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1957FBE-4265-4521-9B22-3381C42EB967}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="1288143"/>
+          <a:ext cx="10490190" cy="5384245"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1888,7 +2780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A911C451-4F5E-414A-9389-A33A7B867661}">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -1910,45 +2802,45 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="C1" s="18"/>
+      <c r="B1" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="33"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="E1" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36"/>
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="37">
         <v>1</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -1967,31 +2859,31 @@
       <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>46084</v>
       </c>
-      <c r="F6" s="27"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
+      <c r="H6" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
@@ -2022,455 +2914,455 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="31" t="s">
+      <c r="J11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="K11" s="31" t="s">
+      <c r="K11" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L11" s="31" t="s">
+      <c r="L11" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="31" t="s">
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="K12" s="31" t="s">
+      <c r="K12" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L12" s="31" t="s">
+      <c r="L12" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="31" t="s">
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="K13" s="31" t="s">
+      <c r="K13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="L13" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="K14" s="31" t="s">
+      <c r="K14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L14" s="31" t="s">
+      <c r="L14" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:12" ht="87" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="31" t="s">
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="31" t="s">
+      <c r="K15" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L15" s="31" t="s">
+      <c r="L15" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="31" t="s">
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="31" t="s">
+      <c r="K16" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="31" t="s">
+      <c r="L16" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="31" t="s">
+      <c r="K17" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="31" t="s">
+      <c r="L17" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="31" t="s">
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="31" t="s">
+      <c r="K18" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L18" s="31" t="s">
+      <c r="L18" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="31" t="s">
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="K19" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L19" s="31" t="s">
+      <c r="L19" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="K20" s="31" t="s">
+      <c r="K20" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L20" s="31" t="s">
+      <c r="L20" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="31" t="s">
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="K21" s="31" t="s">
+      <c r="K21" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L21" s="31" t="s">
+      <c r="L21" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="31" t="s">
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="K22" s="31" t="s">
+      <c r="K22" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L22" s="31" t="s">
+      <c r="L22" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="J23" s="31" t="s">
+      <c r="J23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="K23" s="31" t="s">
+      <c r="K23" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L23" s="31" t="s">
+      <c r="L23" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="31" t="s">
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K24" s="31" t="s">
+      <c r="K24" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L24" s="31" t="s">
+      <c r="L24" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="31" t="s">
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="K25" s="31" t="s">
+      <c r="K25" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L25" s="31" t="s">
+      <c r="L25" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="I26" s="32" t="s">
+      <c r="I26" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="J26" s="31" t="s">
+      <c r="J26" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="31" t="s">
+      <c r="K26" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L26" s="31" t="s">
+      <c r="L26" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="31" t="s">
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="K27" s="31" t="s">
+      <c r="K27" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L27" s="31" t="s">
+      <c r="L27" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="31" t="s">
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="K28" s="31" t="s">
+      <c r="K28" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L28" s="31" t="s">
+      <c r="L28" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H29" s="32" t="s">
+      <c r="H29" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="32" t="s">
+      <c r="I29" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="J29" s="31" t="s">
+      <c r="J29" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="31" t="s">
+      <c r="K29" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L29" s="31" t="s">
+      <c r="L29" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="31" t="s">
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="K30" s="31" t="s">
+      <c r="K30" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L30" s="31" t="s">
+      <c r="L30" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="31" t="s">
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="K31" s="31" t="s">
+      <c r="K31" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L31" s="31" t="s">
+      <c r="L31" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H32" s="32" t="s">
+      <c r="H32" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="J32" s="31" t="s">
+      <c r="J32" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="K32" s="31" t="s">
+      <c r="K32" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L32" s="31" t="s">
+      <c r="L32" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="31" t="s">
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="K33" s="31" t="s">
+      <c r="K33" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L33" s="31" t="s">
+      <c r="L33" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="31" t="s">
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="K34" s="31" t="s">
+      <c r="K34" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L34" s="31" t="s">
+      <c r="L34" s="17" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2480,437 +3372,430 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="37" t="s">
+      <c r="A37" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="37" t="s">
+      <c r="E37" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="37" t="s">
+      <c r="G37" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="H37" s="37" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="31" t="s">
+      <c r="H38" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" s="31" t="s">
+      <c r="D39" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F38" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="G38" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" s="31" t="s">
+      <c r="F44" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" s="31" t="s">
+    <row r="45" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="31" t="s">
+      <c r="D45" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" s="31" t="s">
+    <row r="46" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H40" s="31" t="s">
+      <c r="D46" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H46" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="31" t="s">
+    <row r="47" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="G41" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H41" s="31" t="s">
+      <c r="D47" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="31" t="s">
+    <row r="48" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="F42" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="G42" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H42" s="31" t="s">
+      <c r="D48" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="31" t="s">
+    <row r="49" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H43" s="31" t="s">
+      <c r="D49" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="31" t="s">
+    <row r="50" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D44" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E44" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="F44" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="G44" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H44" s="31" t="s">
+      <c r="D50" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H50" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H45" s="31"/>
-    </row>
-    <row r="46" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C46" s="31" t="s">
+    <row r="51" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D51" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E46" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F46" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="G46" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H46" s="31" t="s">
+      <c r="F51" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H51" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C47" s="31" t="s">
+    <row r="52" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H47" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F48" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H48" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E49" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H49" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="B50" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E50" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F50" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H50" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E51" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F51" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H51" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F52" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G52" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H52" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="B53" s="31" t="s">
+      <c r="D52" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C53" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D53" s="31" t="s">
+      <c r="E52" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="E53" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="G53" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H53" s="31" t="s">
+      <c r="G52" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="H52" s="17" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="I26:I28"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:K2"/>
     <mergeCell ref="H29:H31"/>
     <mergeCell ref="I29:I31"/>
     <mergeCell ref="H32:H34"/>
@@ -2927,13 +3812,6 @@
     <mergeCell ref="I14:I16"/>
     <mergeCell ref="H17:H19"/>
     <mergeCell ref="I17:I19"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="I26:I28"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2962,45 +3840,45 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="18"/>
+      <c r="B1" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="33"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="E1" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36"/>
     </row>
     <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="37">
         <v>1</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -3019,315 +3897,315 @@
       <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>46049</v>
       </c>
-      <c r="F6" s="27"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
+      <c r="H6" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
+      <c r="A9" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="C10" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="F10" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="G10" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="H10" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="I10" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="I10" s="15" t="s">
-        <v>184</v>
-      </c>
       <c r="J10" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="L10" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="M10" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="O10" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="O10" s="15" t="s">
+      <c r="P10" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="Q10" s="15" t="s">
         <v>223</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="K11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="N11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="O11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="P11" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="Q11" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="G12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="H12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="I12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="J12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="N12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="O12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="P12" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="Q12" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="O12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="P12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="E13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="F13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="I13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="J13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="N13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="P13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="Q13" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="D14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="F14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="H14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="I14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="J14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="K14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="L14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="N14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="O14" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="O14" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="P14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q14" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
@@ -3342,25 +4220,25 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
@@ -3371,7 +4249,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -3380,27 +4258,27 @@
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
       <c r="H17" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O17" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -3413,10 +4291,10 @@
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
@@ -3425,7 +4303,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3442,190 +4320,190 @@
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
       <c r="P19" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q19" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I20" s="16"/>
       <c r="J20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K20" s="16"/>
       <c r="L20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M20" s="16"/>
       <c r="N20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q20" s="16"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A22" s="40" t="s">
-        <v>234</v>
+      <c r="A22" s="23" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>182</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="F25" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="G25" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E25" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="H25" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C26" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="E26" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F26" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="F26" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="G26" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>186</v>
-      </c>
       <c r="D27" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="H27" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -3636,15 +4514,15 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
@@ -3652,23 +4530,23 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -3676,13 +4554,13 @@
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
       <c r="G32" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -3691,33 +4569,33 @@
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
       <c r="H33" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -3730,238 +4608,238 @@
         <v>24</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="D39" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="E39" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="F39" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="G39" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="H39" s="12" t="s">
         <v>215</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="C40" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="D40" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>193</v>
       </c>
       <c r="E40" s="16">
         <v>200</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="D41" s="16" t="s">
         <v>196</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>197</v>
       </c>
       <c r="E41" s="16">
         <v>200</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B42" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>192</v>
-      </c>
       <c r="D42" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E42" s="16">
         <v>200</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B43" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>202</v>
-      </c>
       <c r="C43" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E43" s="16">
         <v>200</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C44" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>193</v>
       </c>
       <c r="E44" s="16">
         <v>200</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C45" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" s="16" t="s">
         <v>196</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>197</v>
       </c>
       <c r="E45" s="16">
         <v>200</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E46" s="16">
         <v>200</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C47" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="16" t="s">
         <v>196</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>197</v>
       </c>
       <c r="E47" s="16">
         <v>600</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
@@ -3971,7 +4849,7 @@
     </row>
     <row r="52" spans="1:6" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
@@ -3998,7 +4876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E447681E-DE3A-44C2-B0D1-3B8EA5BE633F}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -4018,45 +4896,45 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="18"/>
+      <c r="B1" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" s="33"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="E1" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36"/>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="37">
         <v>1</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -4075,435 +4953,726 @@
       <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>46084</v>
       </c>
-      <c r="F6" s="27"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="42"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="42"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="42"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="42"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="42"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="42"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+    </row>
+    <row r="30" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-    </row>
-    <row r="9" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
+      <c r="B31" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="E31" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="F31" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="G31" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="G10" s="16" t="s">
+    </row>
+    <row r="32" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="16" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
+      <c r="B32" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="E32" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="F32" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G32" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G11" s="16" t="s">
+    </row>
+    <row r="33" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
+      <c r="B33" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="D33" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="E33" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="F33" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G33" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G12" s="16" t="s">
+    </row>
+    <row r="34" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="16" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
+      <c r="B34" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="E34" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F34" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G34" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G13" s="16" t="s">
+    </row>
+    <row r="35" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="16" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
+      <c r="B35" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="D35" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="E35" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F35" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G35" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G14" s="16" t="s">
+    </row>
+    <row r="36" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A36" s="16" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="58" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
+      <c r="B36" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="D36" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E36" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="E15" s="16" t="s">
+      <c r="F36" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G36" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="F15" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G15" s="16" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="16" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="16" t="s">
+      <c r="B37" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E37" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="F37" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G16" s="16" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A38" s="16" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
+      <c r="B38" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="D38" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="E17" s="16" t="s">
+      <c r="F38" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G38" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" s="16" t="s">
+    </row>
+    <row r="39" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="16" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="B39" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="D39" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="E39" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="F39" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G39" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="F18" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G18" s="16" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="16" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+      <c r="B40" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="D40" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="E40" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="F40" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G40" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G19" s="16" t="s">
+    </row>
+    <row r="41" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="16" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="B41" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="D41" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="E41" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="F41" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G41" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G20" s="16" t="s">
+    </row>
+    <row r="42" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="16" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
+      <c r="B42" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="D42" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="E42" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="F42" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G42" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G21" s="16" t="s">
+    </row>
+    <row r="43" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A43" s="16" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="B43" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="D43" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="E43" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="F43" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="G43" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="G22" s="16" t="s">
+    </row>
+    <row r="44" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A44" s="16" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="B44" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="D44" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="E44" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="F44" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G44" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="F23" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="G23" s="16" t="s">
+    </row>
+    <row r="45" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A45" s="16" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+      <c r="B45" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="D45" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="E45" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="F45" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G45" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="F24" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="G24" s="16" t="s">
+    </row>
+    <row r="46" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="16" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
+      <c r="B46" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="D46" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="E46" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="F46" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G46" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="G25" s="16" t="s">
+    </row>
+    <row r="47" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="16" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="B47" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="D47" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="E47" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="F47" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G47" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="F26" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="G26" s="16" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
         <v>337</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B52" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B59" s="23" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B62" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B63" s="45" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B64" s="45" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B65" s="45" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B66" s="45" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -4517,19 +5686,594 @@
     <mergeCell ref="H2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930C39C1-F3E1-4369-BECF-412E37C44109}">
-  <dimension ref="A1:K27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8B4D89-C168-4BA8-8EBE-D9539DC8A255}">
+  <dimension ref="A1:K62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="37">
+        <v>1</v>
+      </c>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="27">
+        <v>46084</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="G6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>451</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877BDB8E-6AD8-47FA-BBDA-6CFF42AAE722}">
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
@@ -4542,45 +6286,45 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
+      <c r="C1" s="33"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36"/>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="37">
         <v>1</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -4599,494 +6343,398 @@
       <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>46049</v>
       </c>
-      <c r="F6" s="27"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="15" t="s">
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:K2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8B4D89-C168-4BA8-8EBE-D9539DC8A255}">
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="22">
-        <v>1</v>
-      </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="26">
-        <v>46049</v>
-      </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+    <row r="13" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>547</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5103,297 +6751,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877BDB8E-6AD8-47FA-BBDA-6CFF42AAE722}">
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.36328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="22">
-        <v>1</v>
-      </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="26">
-        <v>46049</v>
-      </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:K2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993B51D7-01A3-4330-BCFF-E3274809A9A8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
